--- a/docs/downloads/UAS-5_Skor.xlsx
+++ b/docs/downloads/UAS-5_Skor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\projects\Kominter\all-about-me\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F58CB2-E559-4CA9-974C-B1269DF4AFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05969025-BA2E-4D77-BFC8-AD1024687862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="13896" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -127,12 +127,15 @@
   <si>
     <t>Muhammad Dhafin Faidhulhaq</t>
   </si>
+  <si>
+    <t>Daniel Benaya Toar Supaath</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -169,6 +172,12 @@
       <name val="Source Sans Pro"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -197,13 +206,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,11 +627,11 @@
       <c r="AP2" s="3"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
-        <v>18224055</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>26</v>
+      <c r="A3" s="6">
+        <v>18224047</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="C3" s="2">
         <v>5</v>
@@ -636,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
+        <f>IF(COUNT(C4:F4)=0,"",AVERAGE(C4:F4))</f>
         <v>5</v>
       </c>
       <c r="L3" s="4"/>
@@ -649,10 +659,10 @@
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <v>18224095</v>
+        <v>18224055</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2">
         <v>5</v>
@@ -667,7 +677,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" ref="G4:G5" si="1">IF(COUNT(C4:F4)=0,"",AVERAGE(C4:F4))</f>
+        <f>IF(COUNT(C5:F5)=0,"",AVERAGE(C5:F5))</f>
         <v>5</v>
       </c>
       <c r="L4" s="4"/>
@@ -680,10 +690,10 @@
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>18223103</v>
+        <v>18224095</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2">
         <v>5</v>
@@ -698,7 +708,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="1"/>
+        <f>IF(COUNT(C6:F6)=0,"",AVERAGE(C6:F6))</f>
         <v>5</v>
       </c>
       <c r="L5" s="4"/>
@@ -710,9 +720,26 @@
       <c r="AP5" s="4"/>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A6" s="5">
+        <v>18223103</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <v>5</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -724,7 +751,7 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="G7" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G7:G66" si="0">IF(COUNT(C7:F7)=0,"",AVERAGE(C7:F7))</f>
         <v/>
       </c>
       <c r="L7" s="4"/>
@@ -1504,7 +1531,7 @@
     </row>
     <row r="67" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G67" s="4" t="str">
-        <f t="shared" ref="G67:G82" si="2">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
+        <f t="shared" ref="G67:G82" si="1">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
         <v/>
       </c>
       <c r="L67" s="4"/>
@@ -1517,7 +1544,7 @@
     </row>
     <row r="68" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G68" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L68" s="4"/>
@@ -1530,7 +1557,7 @@
     </row>
     <row r="69" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G69" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L69" s="4"/>
@@ -1543,7 +1570,7 @@
     </row>
     <row r="70" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G70" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L70" s="4"/>
@@ -1556,7 +1583,7 @@
     </row>
     <row r="71" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G71" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L71" s="4"/>
@@ -1569,7 +1596,7 @@
     </row>
     <row r="72" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G72" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L72" s="4"/>
@@ -1582,7 +1609,7 @@
     </row>
     <row r="73" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G73" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L73" s="4"/>
@@ -1595,7 +1622,7 @@
     </row>
     <row r="74" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G74" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L74" s="4"/>
@@ -1608,7 +1635,7 @@
     </row>
     <row r="75" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G75" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L75" s="4"/>
@@ -1621,7 +1648,7 @@
     </row>
     <row r="76" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G76" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L76" s="4"/>
@@ -1634,7 +1661,7 @@
     </row>
     <row r="77" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G77" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L77" s="4"/>
@@ -1647,7 +1674,7 @@
     </row>
     <row r="78" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G78" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L78" s="4"/>
@@ -1660,7 +1687,7 @@
     </row>
     <row r="79" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G79" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L79" s="4"/>
@@ -1673,7 +1700,7 @@
     </row>
     <row r="80" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G80" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L80" s="4"/>
@@ -1686,7 +1713,7 @@
     </row>
     <row r="81" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G81" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L81" s="4"/>
@@ -1699,7 +1726,7 @@
     </row>
     <row r="82" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G82" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L82" s="4"/>
@@ -1712,7 +1739,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F82" xr:uid="{B0F61EF9-DC4B-1D4B-A700-95D0E3F024E2}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C4:F82" xr:uid="{B0F61EF9-DC4B-1D4B-A700-95D0E3F024E2}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
